--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-08-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486CBCEF-21C5-4A4F-BC28-9B933E0855C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9B531A-C7FB-4D15-B0C7-6F2ED877FF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="690" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32595" yWindow="2145" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="384">
   <si>
     <t>SKU</t>
   </si>
@@ -1127,9 +1127,6 @@
   </si>
   <si>
     <t>£48.85</t>
-  </si>
-  <si>
-    <t>£49.35</t>
   </si>
   <si>
     <t>£59.35</t>
@@ -2312,7 +2309,7 @@
         <v>177</v>
       </c>
       <c r="O14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P14" t="s">
         <v>178</v>
@@ -2424,7 +2421,7 @@
         <v>199</v>
       </c>
       <c r="O16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P16" t="s">
         <v>200</v>
@@ -2480,7 +2477,7 @@
         <v>210</v>
       </c>
       <c r="O17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P17" t="s">
         <v>211</v>
@@ -2536,7 +2533,7 @@
         <v>222</v>
       </c>
       <c r="O18" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P18" t="s">
         <v>223</v>
@@ -2648,7 +2645,7 @@
         <v>235</v>
       </c>
       <c r="O20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P20" t="s">
         <v>247</v>
@@ -2704,7 +2701,7 @@
         <v>235</v>
       </c>
       <c r="O21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P21" t="s">
         <v>259</v>
@@ -2757,7 +2754,7 @@
         <v>268</v>
       </c>
       <c r="N22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O22" t="s">
         <v>201</v>
@@ -2928,7 +2925,7 @@
         <v>300</v>
       </c>
       <c r="O25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P25" t="s">
         <v>147</v>
@@ -2984,7 +2981,7 @@
         <v>309</v>
       </c>
       <c r="O26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P26" t="s">
         <v>310</v>
@@ -3037,10 +3034,10 @@
         <v>319</v>
       </c>
       <c r="N27" t="s">
+        <v>378</v>
+      </c>
+      <c r="O27" t="s">
         <v>379</v>
-      </c>
-      <c r="O27" t="s">
-        <v>380</v>
       </c>
       <c r="P27" t="s">
         <v>320</v>
@@ -3093,10 +3090,10 @@
         <v>329</v>
       </c>
       <c r="N28" t="s">
+        <v>380</v>
+      </c>
+      <c r="O28" t="s">
         <v>381</v>
-      </c>
-      <c r="O28" t="s">
-        <v>382</v>
       </c>
       <c r="P28" t="s">
         <v>330</v>
@@ -3149,10 +3146,10 @@
         <v>339</v>
       </c>
       <c r="N29" t="s">
+        <v>382</v>
+      </c>
+      <c r="O29" t="s">
         <v>383</v>
-      </c>
-      <c r="O29" t="s">
-        <v>384</v>
       </c>
       <c r="P29" t="s">
         <v>340</v>
